--- a/data/trans_bre/IP16A05-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16A05-Habitat-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-18,84; 4,97</t>
+          <t>-19,61; 5,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 25,21</t>
+          <t>-8,95; 23,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-30,64; -3,36</t>
+          <t>-30,69; -1,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 16,43</t>
+          <t>-2,15; 18,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 211,81</t>
+          <t>-100,0; 166,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-48,85; 291,13</t>
+          <t>-44,37; 335,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 26,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 15,17</t>
+          <t>-6,23; 15,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-16,78; 10,54</t>
+          <t>-16,75; 9,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 18,24</t>
+          <t>-3,64; 18,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 8,59</t>
+          <t>-8,35; 9,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-50,87; 400,92</t>
+          <t>-51,77; 512,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-67,57; 129,04</t>
+          <t>-68,32; 108,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-31,34; 544,28</t>
+          <t>-33,58; 475,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-75,29; 228,26</t>
+          <t>-74,97; 271,35</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,3; 7,52</t>
+          <t>-14,21; 7,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 22,46</t>
+          <t>-1,06; 22,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-26,38; 3,96</t>
+          <t>-25,92; 4,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 17,0</t>
+          <t>-7,13; 17,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 274,6</t>
+          <t>-100,0; 221,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-20,4; 945,44</t>
+          <t>-33,52; 861,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-84,36; 47,8</t>
+          <t>-88,24; 41,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-78,23; 580,14</t>
+          <t>-74,01; 554,48</t>
         </is>
       </c>
     </row>
@@ -960,37 +960,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,59; 11,61</t>
+          <t>-13,28; 10,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 20,93</t>
+          <t>-7,43; 20,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 17,39</t>
+          <t>-9,61; 16,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 11,46</t>
+          <t>-3,29; 11,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-83,21; 294,58</t>
+          <t>-100,0; 216,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-37,75; 316,97</t>
+          <t>-38,76; 264,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-63,88; 587,14</t>
+          <t>-70,09; 420,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 4,1</t>
+          <t>-7,1; 4,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 12,27</t>
+          <t>-1,72; 11,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 5,05</t>
+          <t>-7,44; 6,3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 8,97</t>
+          <t>-2,34; 9,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-54,63; 55,95</t>
+          <t>-55,29; 58,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 122,81</t>
+          <t>-12,74; 110,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-49,64; 57,54</t>
+          <t>-47,42; 70,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-34,49; 250,83</t>
+          <t>-35,55; 262,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A05-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16A05-Habitat-trans_bre.xlsx
@@ -660,32 +660,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-19,61; 5,39</t>
+          <t>-18,77; 5,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 23,67</t>
+          <t>-9,39; 23,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-30,69; -1,78</t>
+          <t>-31,41; -2,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 18,35</t>
+          <t>-2,36; 17,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 166,13</t>
+          <t>-100,0; 171,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-44,37; 335,77</t>
+          <t>-50,09; 307,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 15,32</t>
+          <t>-6,39; 15,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-16,75; 9,55</t>
+          <t>-18,55; 10,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 18,68</t>
+          <t>-4,09; 19,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 9,03</t>
+          <t>-8,14; 9,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-51,77; 512,59</t>
+          <t>-56,59; 428,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-68,32; 108,91</t>
+          <t>-72,87; 125,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-33,58; 475,14</t>
+          <t>-38,72; 484,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-74,97; 271,35</t>
+          <t>-70,05; 283,37</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,21; 7,82</t>
+          <t>-16,1; 7,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 22,73</t>
+          <t>0,03; 21,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-25,92; 4,04</t>
+          <t>-26,75; 2,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 17,03</t>
+          <t>-8,27; 17,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 221,79</t>
+          <t>-100,0; 183,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-33,52; 861,42</t>
+          <t>-25,82; 828,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-88,24; 41,84</t>
+          <t>-85,3; 38,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-74,01; 554,48</t>
+          <t>-76,14; 569,04</t>
         </is>
       </c>
     </row>
@@ -960,37 +960,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,28; 10,58</t>
+          <t>-12,65; 11,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 20,29</t>
+          <t>-6,21; 19,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 16,03</t>
+          <t>-8,86; 17,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 11,45</t>
+          <t>-4,33; 11,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 216,56</t>
+          <t>-100,0; 217,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-38,76; 264,78</t>
+          <t>-36,67; 313,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-70,09; 420,42</t>
+          <t>-69,94; 505,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 4,3</t>
+          <t>-7,11; 4,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 11,24</t>
+          <t>-1,7; 11,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 6,3</t>
+          <t>-7,98; 5,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 9,35</t>
+          <t>-2,05; 9,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-55,29; 58,6</t>
+          <t>-54,61; 58,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,74; 110,81</t>
+          <t>-11,11; 118,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-47,42; 70,09</t>
+          <t>-47,57; 62,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-35,55; 262,05</t>
+          <t>-31,22; 280,6</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A05-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16A05-Habitat-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos antibióticos</t>
+          <t>Menores que consumieron medicamentos antibióticos</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,38</t>
+          <t>4,9</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>239,78%</t>
+          <t>198,27%</t>
         </is>
       </c>
     </row>
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-18,77; 5,95</t>
+          <t>-18,84; 4,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,39; 23,51</t>
+          <t>-9,06; 25,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-31,41; -2,13</t>
+          <t>-30,64; -3,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 17,29</t>
+          <t>-3,41; 16,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 171,02</t>
+          <t>-100,0; 211,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-50,09; 307,77</t>
+          <t>-48,85; 291,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 26,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0,39</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 15,15</t>
+          <t>-5,54; 15,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-18,55; 10,12</t>
+          <t>-16,78; 10,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 19,11</t>
+          <t>-3,75; 18,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 9,37</t>
+          <t>-9,44; 9,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-56,59; 428,14</t>
+          <t>-50,87; 400,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-72,87; 125,04</t>
+          <t>-67,57; 129,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-38,72; 484,48</t>
+          <t>-31,34; 544,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-70,05; 283,37</t>
+          <t>-74,89; 234,7</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,08</t>
+          <t>4,26</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>71,55%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-16,1; 7,3</t>
+          <t>-14,3; 7,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,03; 21,96</t>
+          <t>-0,76; 22,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-26,75; 2,9</t>
+          <t>-26,38; 3,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 17,25</t>
+          <t>-5,33; 12,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 183,4</t>
+          <t>-100,0; 274,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-25,82; 828,76</t>
+          <t>-20,4; 945,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-85,3; 38,37</t>
+          <t>-84,36; 47,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-76,14; 569,04</t>
+          <t>-62,76; 556,59</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,38</t>
+          <t>3,82</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>158,06%</t>
+          <t>207,99%</t>
         </is>
       </c>
     </row>
@@ -960,37 +960,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,65; 11,47</t>
+          <t>-11,59; 11,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 19,96</t>
+          <t>-6,16; 20,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 17,12</t>
+          <t>-8,98; 17,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 11,06</t>
+          <t>-2,01; 12,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 217,12</t>
+          <t>-83,21; 294,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-36,67; 313,74</t>
+          <t>-37,75; 316,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-69,94; 505,57</t>
+          <t>-63,88; 587,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,07</t>
+          <t>2,91</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>53,8%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 4,15</t>
+          <t>-7,03; 4,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 11,68</t>
+          <t>-1,44; 12,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 5,69</t>
+          <t>-7,9; 5,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 9,4</t>
+          <t>-2,1; 7,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-54,61; 58,83</t>
+          <t>-54,63; 55,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,11; 118,22</t>
+          <t>-10,51; 122,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-47,57; 62,0</t>
+          <t>-49,64; 57,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-31,22; 280,6</t>
+          <t>-30,09; 227,5</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A05-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16A05-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,191 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-5,55</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>7,1</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-13,62</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4,9</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-46,93%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>48,71%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-84,58%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>198,27%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-0.7306367689899947</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1.646843679260358</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-2.17734841259194</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>1.118298456105464</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.3298228153475222</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.5078600182380834</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.8278844729709838</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>2.314255518511374</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-18,84; 4,97</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-9,06; 25,21</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-30,64; -3,36</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-3,41; 16,05</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 211,81</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-48,85; 291,13</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 26,2</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-3.178915834603196</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-2.188326387468342</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-5.00580004348031</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-0.5543040137392617</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.5764046177590345</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1.513338213365976</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>6.172584156031421</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>-0.1256490650419955</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>3.56507197855379</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>2.549619379552523</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>3.329562859432313</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>4,44</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-3,11</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>7,85</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,39</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>56,57%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-17,74%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>89,88%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>4,72%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-5,54; 15,17</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-16,78; 10,54</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-3,75; 18,24</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-9,44; 9,55</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-50,87; 400,92</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-67,57; 129,04</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-31,34; 544,28</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-74,89; 234,7</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>1.094366183919389</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.2575688097475486</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.814340967697808</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-0.2743103095275017</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.7159915354769406</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.08147241432434642</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>1.133083499014248</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.1400648983954248</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-3,85</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>10,3</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-10,08</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,26</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-34,96%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>162,32%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-48,11%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>71,55%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-1.107811376644154</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-3.173970719042843</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-0.3918745716421197</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-2.649495518212561</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.532265623393596</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.7015061717956907</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.3142878894317123</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.7671756341583166</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-14,3; 7,52</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-0,76; 22,46</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-26,38; 3,96</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-5,33; 12,99</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 274,6</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-20,4; 945,44</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-84,36; 47,8</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-62,76; 556,59</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>3.331711574084356</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2.336852553339392</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>4.151806091722579</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>1.685007467599246</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>4.87581340100447</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.284378110193591</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>6.786578026497361</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>2.255397192453626</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +811,293 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-2,3</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>6,45</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3,74</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3,82</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-21,37%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>50,03%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>41,04%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>207,99%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-1.277467226222568</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>2.155219679475491</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.571332720794147</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1.488614213077867</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.4939590784803068</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>1.566417013649227</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.4494534360594026</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.8048178382549961</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-11,59; 11,61</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-6,16; 20,93</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-8,98; 17,39</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-2,01; 12,43</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-83,21; 294,58</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-37,75; 316,97</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-63,88; 587,14</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-3.948606014251551</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-0.105205668303226</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-4.627073914577032</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-1.30425964933144</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.3099598267943736</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.8697316003334035</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.5965707746934839</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.9449805937561186</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>5.199760292178043</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1.036847713159185</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>4.635507828152964</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>1.571119983897309</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>9.298319468317858</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.7116832779265976</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>5.909482129768355</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.97216529644032</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.9003358082297821</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.6955224350044826</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.6642196979041908</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.4835498707771125</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.3059429415563844</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.521521749680529</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>1.943326811953906</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-3.01271927413519</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-1.785652753882936</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-1.106251234207984</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-0.3866460004685071</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.4708370736168992</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.7118604716099599</v>
+      </c>
+      <c r="J14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.059343459244201</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>4.1953988166272</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>3.098322022095168</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>2.314115442745343</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>1.697989079931638</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>2.964833352865702</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>7.062592247924449</v>
+      </c>
+      <c r="J15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-1,3</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>4,9</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-1,34</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,91</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-12,74%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>37,84%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-10,28%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>53,8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-7,03; 4,1</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-1,44; 12,27</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-7,9; 5,05</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-2,1; 7,83</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-54,63; 55,95</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-10,51; 122,81</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-49,64; 57,54</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-30,09; 227,5</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-0.3935494938689252</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.983974345583465</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.04114815518994029</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.6209154895944783</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.1937165461528148</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.3612848422709916</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.01908667176998525</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.4866226165491471</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-1.535960186514303</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-0.6402136029516783</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.224466549254025</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-0.509848395882897</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.5805646871208628</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.2092512475285082</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.4424791810761384</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.3216714147355654</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.725843034869579</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.46752277807275</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.172567130902131</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>1.788997790296643</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.4961060528826097</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1.199654600483328</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.8146357680153501</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>2.311469162961169</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1105,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
